--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-003_退勤打刻_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-003_退勤打刻_オンライン詳細設計書.xlsx
@@ -333,7 +333,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="10896600"/>
+    <ext cx="8572500" cy="11096625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜022)の概要。本書はそのうち ONL-003 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-003 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr"/>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="64" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -1983,7 +1983,8 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>・確定設計変更 D1〜D10 を反映：updated_at をトリガ自動更新に変更、トークン不正を 401 / E-001 の JSON に更新</t>
+          <t>・確定設計変更 D1〜D10 を反映：updated_at をトリガ自動更新に変更、トークン不正を 401 / E-001 の JSON に更新
+・実装に合わせて逆反映：Controller は Authentication#getName() でユーザーIDを取得、トークン有効期限を2時間に更新（コードを正とする）</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
@@ -3194,7 +3195,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Controller: Long.valueOf(jwt.getSubject())。リクエストに userId は含めない</t>
+          <t>Controller: Long.valueOf(auth.getName())。リクエストに userId は含めない</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -3483,7 +3484,7 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>public ClockOutResponse clockOut(@AuthenticationPrincipal Jwt jwt)</t>
+          <t>public ClockOutResponse clockOut(Authentication auth)</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -3547,17 +3548,17 @@
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>認証済みトークン（Spring Security が注入）。sub = users.id</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D8" s="9" t="n"/>
@@ -3604,7 +3605,7 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>1. Long userId = Long.valueOf(jwt.getSubject());
+          <t>1. Long userId = Long.valueOf(auth.getName());
 2. return attendanceService.clockOut(userId);</t>
         </is>
       </c>

--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-003_退勤打刻_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-003_退勤打刻_オンライン詳細設計書.xlsx
@@ -273,7 +273,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10953750" cy="3895725"/>
+    <ext cx="10953750" cy="4943475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -303,7 +303,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10953750" cy="9744075"/>
+    <ext cx="10953750" cy="11620500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -330,10 +330,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>16</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="11096625"/>
+    <ext cx="8572500" cy="13163550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-003 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜026)の概要。本書はそのうち ONL-003 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -787,7 +787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E20"/>
+  <dimension ref="A2:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -892,186 +892,210 @@
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
+          <t>E-022</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>休憩中・離席中は退勤できません。先に休憩（離席）を終了してください。</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>継続中（end_at が NULL）の休憩・離席の区間がある</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>AttendanceService#clockOut</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="64" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>E-001</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>認証が必要です。再度ログインしてください。</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>JWT なし・不正・期限切れ、パスワード変更後の旧トークン、無効ユーザー（AuthenticationEntryPoint / ActiveUserFilter。Controller には到達しない）</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>SecurityConfig</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
           <t>E-012</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>システムエラーが発生しました。しばらくしてから再度お試しください。</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>上記以外の予期しない例外（DB 接続断・ロック待ちタイムアウトなど）</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>GlobalExceptionHandler#handleOther</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>8.2 ログ出力</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="10" t="n"/>
-    </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="19" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>レベル</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>タイミング</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>出力内容</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>出力禁止</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>出力箇所</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>退勤打刻が成功したとき</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Clock-out: userId={}, workDate={}, workMinutes={}, overtimeMinutes={}</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>氏名・メールアドレス・JWT</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>AttendanceService#clockOut</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="49" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="13" ht="49" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>予期しない例外（E-012）</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Unexpected error ＋スタックトレース</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>JWT・リクエストヘッダ</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>GlobalExceptionHandler</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="49" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="14" ht="64" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>E-006 / E-007（業務エラー）</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>E-006 / E-007 / E-022（業務エラー）</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>出力しない（業務上想定内のため）</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>8.3 セキュリティ・権限上の考慮</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="10" t="n"/>
-    </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>本人のデータのみ</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>更新対象は「JWT の sub のユーザー」かつ「本日の work_date」の行だけ（WHERE user_id = ? AND work_date = ?）。他人の打刻行は ID を指定する手段がなく、変更できない。全ロール可（@PreAuthorize なし、authenticated のみ）。</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="10" t="n"/>
-    </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>時刻の信頼</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>退勤時刻・勤務時間・残業時間はすべてサーバー側で計算する。クライアントから時刻・時間数は受け取らない。訂正は打刻修正申請（ONL-005/010）のみ。</t>
-        </is>
-      </c>
+      <c r="B16" s="9" t="n"/>
       <c r="C16" s="9" t="n"/>
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="10" t="n"/>
@@ -1079,12 +1103,12 @@
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>二重実行（二重退勤）</t>
+          <t>本人のデータのみ</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>行ロック（FOR UPDATE）＋ clock_out の NULL 判定で、連打・複数タブ・同時リクエストでも退勤は1回だけ記録される（後続は E-006）。画面側でも API 呼び出し中はボタンを非活性にする（KF-BD-012）。</t>
+          <t>更新対象は「JWT の sub のユーザー」かつ「本日の work_date」の行だけ（WHERE user_id = ? AND work_date = ?）。他人の打刻行は ID を指定する手段がなく、変更できない。全ロール可（@PreAuthorize なし、authenticated のみ）。</t>
         </is>
       </c>
       <c r="C17" s="9" t="n"/>
@@ -1094,12 +1118,12 @@
     <row r="18" ht="34" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>タイムゾーン</t>
+          <t>時刻の信頼</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>today と clock_out は Clock Bean（Asia/Tokyo）から取得する。work_date の判定も JST。JVM/OS が UTC でも結果は変わらない。応答の clockOut は +09:00 付き。</t>
+          <t>退勤時刻・勤務時間・残業時間はすべてサーバー側で計算する。クライアントから時刻・時間数は受け取らない。訂正は打刻修正申請（ONL-005/010）のみ。</t>
         </is>
       </c>
       <c r="C18" s="9" t="n"/>
@@ -1109,12 +1133,12 @@
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>既知の制約</t>
+          <t>二重実行（二重退勤）</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>日跨ぎ勤務（深夜0時を越える勤務）は未対応。前日出勤・未退勤の行は翌日の退勤打刻では更新されず E-007（打刻修正申請で補正）。INACTIVE ユーザーのトークンは有効期限内なら使える（ONL-001 と同じ）。</t>
+          <t>行ロック（FOR UPDATE）＋ clock_out の NULL 判定で、連打・複数タブ・同時リクエストでも退勤は1回だけ記録される（後続は E-006）。画面側でも API 呼び出し中はボタンを非活性にする（KF-BD-012）。</t>
         </is>
       </c>
       <c r="C19" s="9" t="n"/>
@@ -1124,29 +1148,59 @@
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>決定事項</t>
+          <t>タイムゾーン</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>①成功時は 200（更新のため）。②E-006/E-007 は 409。③休憩は 6h超45分・8h超60分を自動控除（KF-DD-001 に従う）。画面イメージ(SCR-103)の数値例とは一致しないが設計書の規則を正とする。④AttendanceCalculator は ONL-010（打刻修正承認時の再計算）でも使う共有部品。</t>
+          <t>today と clock_out は Clock Bean（Asia/Tokyo）から取得する。work_date の判定も JST。JVM/OS が UTC でも結果は変わらない。応答の clockOut は +09:00 付き。</t>
         </is>
       </c>
       <c r="C20" s="9" t="n"/>
       <c r="D20" s="9" t="n"/>
       <c r="E20" s="10" t="n"/>
     </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>既知の制約</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>日跨ぎ勤務（深夜0時を越える勤務）は未対応。前日出勤・未退勤の行は翌日の退勤打刻では更新されず E-007（打刻修正申請で補正）。INACTIVE ユーザー・パスワード変更後の旧トークンは ActiveUserFilter により 401 / E-001 になる。</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="49" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>決定事項</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>①成功時は 200（更新のため）。②E-006/E-007 は 409。③休憩は、打刻がある日は打刻合計、ない日は 6h超45分・8h超60分を自動控除。日中離席（AWAY）は全て控除。画面イメージ(SCR-103)の数値例とは一致しないが設計書の規則を正とする。④AttendanceCalculator は ONL-010（打刻修正承認時の再計算）でも使う共有部品。 ⑤休憩中・離席中の退勤は E-022 で拒否（控除漏れ防止）。</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="10" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B20:E20"/>
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="B21:E21"/>
     <mergeCell ref="B19:E19"/>
-    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B22:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1159,7 +1213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E32"/>
+  <dimension ref="A2:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1172,7 +1226,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>9.1 AttendanceCalculator#calculate（JUnit・パラメータ化）</t>
+          <t>9.1 AttendanceCalculator#calculate（JUnit・パラメータ化。区間なし／区間あり）</t>
         </is>
       </c>
       <c r="B2" s="9" t="n"/>
@@ -1450,367 +1504,418 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>区間あり：09:00 → 18:00、BREAK 12:00-13:00</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>休憩 60（打刻）、勤務 480、残業 0</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>打刻した休憩を控除</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>境界</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>BREAK 12:00-12:30（法定より短い）</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>休憩 30（打刻値）、勤務 510、残業 30</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>打刻どおり控除（法定へ補正しない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>AWAY 14:00-15:00 のみ（休憩の打刻なし）</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>離席 60 控除、net=480 → 法定 45、勤務 435</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>離席は全て控除。法定は net で判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>BREAK 60 分 ＋ AWAY 30 分</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>勤務 450（540−30−60）</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>境界</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>継続中の区間（end=NULL）</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>計算に入らない。休憩の打刻なし扱い（法定）</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>open span ignored</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>境界</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>区間が出勤前／退勤後にはみ出す</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>出勤〜退勤の範囲に切り詰めて数える。範囲外のみなら 0 分</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>clip の検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>境界</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>AWAY で net が 360 分以下になる（09:00-16:00・AWAY 90 分）</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>法定休憩 0。勤務 330</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>離席を引いた後で法定判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>9.2 AttendanceService#clockOut（Mockito・Clock 固定 2026-10-03 18:30 JST）</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="10" t="n"/>
-    </row>
-    <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>観点・条件</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>期待結果</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>行あり clock_in=09:00・clock_out=NULL</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>clock_out=18:30:00、work=510、overtime=30 で saveAndFlush。応答に3項目</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>Calculator は実物またはモック</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>異常</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>本日の行がない</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>BusinessException E-007 / 409</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>save は呼ばれない</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>異常</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>行はあるが clock_in が NULL</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>BusinessException E-007 / 409</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>異常</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>clock_out が既にある</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>BusinessException E-006 / 409</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>値は変更されない</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>境界</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>E-007 と E-006 の両方に当てはまる条件（clock_in なし・clock_out あり）</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>E-007 が優先</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>判定順の確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>境界</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>now が clock_in より前（clock_in = 18:31）</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>clock_out = clock_in に補正、work=0、overtime=0</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>異常時の防御</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>境界</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>昨日（10/02）の未退勤行のみ存在</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>E-007（本日の行がないため）</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>日跨ぎ未対応の確認。昨日の行は不変</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>9.3 AttendanceController / 結合テスト</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="10" t="n"/>
-    </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>観点・条件</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>有効 JWT で POST（出勤済み）</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>200、body に clockOut(+09:00付き) / workMinutes / overtimeMinutes</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr"/>
     </row>
     <row r="27" ht="34" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>異常</t>
+          <t>境界</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>トークンなし</t>
+          <t>E-007 と E-006 の両方に当てはまる条件（clock_in なし・clock_out あり）</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>401 / E-001（AuthenticationEntryPoint の JSON）</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28" ht="19" customHeight="1">
+          <t>E-007 が優先</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>判定順の確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>異常</t>
+          <t>境界</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>出勤前に退勤</t>
+          <t>now が clock_in より前（clock_in = 18:31）</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>409 E-007 のエラー JSON</t>
+          <t>clock_out = clock_in に補正、work=0、overtime=0</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>fieldErrors は空配列</t>
+          <t>異常時の防御</t>
         </is>
       </c>
     </row>
     <row r="29" ht="34" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>異常</t>
+          <t>境界</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>退勤を2回続けて実行</t>
+          <t>昨日（10/02）の未退勤行のみ存在</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>1回目 200、2回目 409 E-006。DB の clock_out / work_minutes は1回目のまま</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr"/>
+          <t>E-007（本日の行がないため）</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>日跨ぎ未対応の確認。昨日の行は不変</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="34" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -1820,79 +1925,371 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
+          <t>継続中の休憩（BREAK）がある状態で退勤</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>BusinessException E-022 / 409。save は呼ばれない。clock_out は変更されない</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>clockOut_whileBreaking_isRejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>継続中の離席（AWAY）がある状態で退勤</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>E-022 / 409</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>終了済みの BREAK 12:00-13:00 がある状態で退勤（18:30）</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>work=510、overtime=30（拘束570−休憩60）。calculate に spans が渡る</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>区間を反映した保存値の確認（ArgumentCaptor）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>境界</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>E-006 と E-022 の両方に当てはまる条件（clock_out あり・継続中あり）</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>E-006 が優先</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>判定順 E-007 → E-006 → E-022</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>9.3 AttendanceController / 結合テスト</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="10" t="n"/>
+    </row>
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>観点・条件</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>有効 JWT で POST（出勤済み）</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>200、body に clockOut(+09:00付き) / workMinutes / overtimeMinutes</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>トークンなし</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>401 / E-001（AuthenticationEntryPoint の JSON）</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39" ht="19" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>出勤前に退勤</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>409 E-007 のエラー JSON</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>fieldErrors は空配列</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>退勤を2回続けて実行</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>1回目 200、2回目 409 E-006。DB の clock_out / work_minutes は1回目のまま</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
           <t>同一ユーザーが2スレッドで同時に退勤（PostgreSQL / Testcontainers）</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>一方 200、他方 409 E-006。clock_out は1回だけ書かれる</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>FOR UPDATE の検証</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>出勤 → 退勤の連続（ONL-002 → ONL-003）</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>DB の1行に clock_in / clock_out / work / overtime が揃う。created_at は不変</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>結合</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>他ユーザーの行が存在する状態で退勤</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>自分の行だけが更新される</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>user_id 条件の確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="49" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>開始（ONL-024）→ 終了（ONL-025）→ 退勤の連続</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>DB の 1 行に clock_in / clock_out / work / overtime が揃い、attendance_breaks の区間が勤務時間に反映される</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>結合</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>休憩開始後に退勤（終了せず）</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>409 E-022。その後、休憩終了 → 退勤は 200</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>結合</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A35:E35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1905,7 +2302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2385,29 @@
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4" ht="109" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席対応に合わせて更新：継続中の休憩・離席がある場合の退勤を E-022（409）で拒否する判定（⑥）と区間取得（⑧）を処理フローに追加し、AttendanceCalculator#calculate を区間つきの 3 引数版（BREAK は打刻合計、無ければ法定休憩を自動控除／AWAY は全て控除）に更新。使用テーブルに attendance_breaks（R）を追加、計算例・単体テスト観点・エラー一覧を更新。401 のメッセージを実装に合わせて「認証が必要です。再度ログインしてください。」に修正</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2001,7 +2421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F35"/>
+  <dimension ref="A2:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2088,7 +2508,7 @@
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="10" t="n"/>
     </row>
-    <row r="7" ht="19" customHeight="1">
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>目的</t>
@@ -2096,7 +2516,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>ログインユーザー本人の「本日分」の退勤時刻をサーバー時刻（Asia/Tokyo）で記録し、休憩を控除した勤務時間と残業時間（分）を計算して保存する。</t>
+          <t>ログインユーザー本人の「本日分」の退勤時刻をサーバー時刻（Asia/Tokyo）で記録し、休憩・日中離席の打刻（ONL-024/025）を反映して勤務時間と残業時間（分）を計算して保存する。休憩中・離席中（継続中の区間がある間）は退勤できない。</t>
         </is>
       </c>
       <c r="C7" s="9" t="n"/>
@@ -2120,7 +2540,7 @@
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="10" t="n"/>
     </row>
-    <row r="9" ht="19" customHeight="1">
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
           <t>事前条件</t>
@@ -2128,7 +2548,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>有効な JWT を持つ。本日（JST）の attendance_records に当該ユーザーの行があり、clock_in が設定済みで clock_out が NULL（出勤済み・退勤未打刻）。</t>
+          <t>有効な JWT を持つ。本日（JST）の attendance_records に当該ユーザーの行があり、clock_in が設定済みで clock_out が NULL（出勤済み・退勤未打刻）。かつ、その行に end_at が NULL の attendance_breaks 行（継続中の休憩・離席）がない。</t>
         </is>
       </c>
       <c r="C9" s="9" t="n"/>
@@ -2136,7 +2556,7 @@
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="10" t="n"/>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="49" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t>事後条件</t>
@@ -2144,7 +2564,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>本日の attendance_records 行の clock_out = 現在時刻、work_minutes = 勤務時間（分）、overtime_minutes = 残業時間（分）が設定される。レスポンスにこの3項目を返す。</t>
+          <t>本日の attendance_records 行の clock_out = 現在時刻、work_minutes = 勤務時間（分）、overtime_minutes = 残業時間（分）が設定される。勤務時間は拘束時間から日中離席（AWAY）の合計を引き、さらに休憩を引いたもの（休憩の打刻がある日は打刻した合計、ない日は法定休憩を自動控除）。レスポンスにこの3項目を返す。attendance_breaks は更新しない。</t>
         </is>
       </c>
       <c r="C10" s="9" t="n"/>
@@ -2160,7 +2580,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>attendance_records: R/U</t>
+          <t>attendance_records: R/U / attendance_breaks: R</t>
         </is>
       </c>
       <c r="C11" s="9" t="n"/>
@@ -2168,7 +2588,7 @@
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="10" t="n"/>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="49" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
         <is>
           <t>トランザクション</t>
@@ -2176,7 +2596,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>更新あり（AttendanceService#clockOut に @Transactional）。行ロック付き検索〜UPDATE を1トランザクションで行う。同時の二重退勤は行ロックで直列化し、後続は E-006 になる。</t>
+          <t>更新あり（AttendanceService#clockOut に @Transactional）。行ロック付き検索〜継続中の区間の確認〜区間の取得〜UPDATE を1トランザクションで行う。同時の二重退勤は行ロックで直列化し、後続は E-006 になる。休憩・離席の開始/終了（ONL-024/025）も同じ打刻行をロックするため、退勤と区間の更新は同時には進まない。</t>
         </is>
       </c>
       <c r="C12" s="9" t="n"/>
@@ -2249,7 +2669,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>E-006 / E-007 / I-002（I-002 は画面側で表示）／E-012</t>
+          <t>E-006 / E-007 / E-022 / I-002（I-002 は画面側で表示）／E-012</t>
         </is>
       </c>
       <c r="D17" s="9" t="n"/>
@@ -2289,7 +2709,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>ONL-003 の概要（勤務時間＝退勤−出勤−休憩、残業＝勤務時間−480分）</t>
+          <t>ONL-003 の概要（勤務時間＝退勤−出勤−休憩−離席、残業＝勤務時間−480分）</t>
         </is>
       </c>
       <c r="D19" s="9" t="n"/>
@@ -2329,7 +2749,7 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>attendance_records テーブル・制約</t>
+          <t>attendance_records / attendance_breaks（V4）テーブル・制約</t>
         </is>
       </c>
       <c r="D21" s="9" t="n"/>
@@ -2349,7 +2769,7 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>AttendanceService / 勤務/残業時間計算</t>
+          <t>AttendanceService / AttendanceCalculator（休憩・離席の控除）</t>
         </is>
       </c>
       <c r="D22" s="9" t="n"/>
@@ -2369,7 +2789,7 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>退勤ボタン・入力チェック No.2, 3（E-007 / E-006）</t>
+          <t>退勤ボタン・入力チェック（E-007 / E-006 / E-022）・休憩中の退勤ボタン非活性</t>
         </is>
       </c>
       <c r="D23" s="9" t="n"/>
@@ -2396,314 +2816,437 @@
       <c r="E24" s="9" t="n"/>
       <c r="F24" s="10" t="n"/>
     </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>1.3 対象クラス一覧（パッケージ：com.example.kintaiflow）</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="9" t="n"/>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>ONL-024</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席開始</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>attendance_breaks への区間の追加（BreakResponse / AttendanceBreakRepository の定義元）</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>ONL-025</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席終了</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>継続中の区間を閉じる。閉じないと本処理は E-022</t>
+        </is>
+      </c>
       <c r="D26" s="9" t="n"/>
       <c r="E26" s="9" t="n"/>
       <c r="F26" s="10" t="n"/>
     </row>
     <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>ONL-010</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>承認</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>打刻修正・休憩離席修正の承認時にも AttendanceCalculator#calculate(in, out, spans) を使って勤務・残業を再計算</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>1.3 対象クラス一覧（パッケージ：com.example.kintaiflow）</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>パッケージ</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>クラス名</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>責務</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>ファイル</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>新規/既存</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>controller</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>AttendanceController</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Controller</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>打刻・月次勤怠の API 入口（本処理で clockOut を追加）</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>controller/AttendanceController.java</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-002 で定義）</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="32" ht="64" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>AttendanceService</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>退勤打刻の業務ロジック（本処理で clockOut を追加）</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>退勤打刻の業務ロジック（本処理で clockOut を追加。休憩・離席の区間取得 spansOf を含む）</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>service/AttendanceService.java</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-002 で定義）</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="49" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="33" ht="79" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>AttendanceCalculator</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>勤務時間・残業時間の計算（休憩控除ルール）。ONL-010（打刻修正の反映）でも共用</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>勤務時間・残業時間の計算（休憩・離席の控除ルール）。calculate(in, out) と calculate(in, out, spans) を持つ。ONL-010（修正の反映）でも共用</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>service/AttendanceCalculator.java</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>新規</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="49" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="34" ht="49" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>repository</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>AttendanceRecordRepository</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Repository</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>行ロック付き検索 findWithLockByUserIdAndWorkDate を共用（追加メソッドなし）</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>repository/AttendanceRecordRepository.java</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-002 で定義）</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="35" ht="94" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>repository</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>AttendanceBreakRepository</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Repository</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>継続中の区間の確認 findFirstByAttendanceRecordIdAndEndAtIsNull と、区間一覧 findByAttendanceRecordIdOrderByStartAtAsc を使用（追加メソッドなし）</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>repository/AttendanceBreakRepository.java</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>既存（ONL-024 で定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>entity</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>AttendanceRecord</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>attendance_records テーブルのマッピング</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>entity/AttendanceRecord.java</t>
         </is>
       </c>
-      <c r="F32" s="7" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-002 で定義）</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="49" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="37" ht="49" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>AttendanceBreak</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>attendance_breaks テーブルのマッピング（kind / startAt / endAt）。本処理は読取りのみ</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>entity/AttendanceBreak.java</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>既存（ONL-024 で定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="49" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>dto</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>ClockOutResponse</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>DTO(record)</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>退勤打刻の正常応答（clockOut, workMinutes, overtimeMinutes）</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>dto/ClockOutResponse.java</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>新規</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="34" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>config</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>ClockConfig / AppTime</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>Configuration / Utility</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>Clock Bean（Asia/Tokyo）／toIso()</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>config/ClockConfig.java, config/AppTime.java</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-002 で定義）</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="34" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>exception</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>BusinessException / GlobalExceptionHandler</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>Exception / ControllerAdvice</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>業務エラーの保持と共通エラー応答への変換</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>exception/*.java</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-001 で定義）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="26">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="C19:F19"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C18:F18"/>
@@ -2713,14 +3256,18 @@
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="C24:F24"/>
+    <mergeCell ref="A29:F29"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C26:F26"/>
     <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C25:F25"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C27:F27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2910,7 +3457,7 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="10" t="n"/>
     </row>
-    <row r="8" ht="19" customHeight="1">
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>workMinutes</t>
@@ -2928,7 +3475,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>退勤−出勤−休憩（分）。休憩控除は 6 時間超 45 分／8 時間超 60 分</t>
+          <t>拘束時間 − 日中離席 − 休憩（分）。休憩の打刻がある日は打刻した合計、ない日は法定休憩（6 時間超 45 分／8 時間超 60 分）を自動控除</t>
         </is>
       </c>
       <c r="E8" s="9" t="n"/>
@@ -3086,7 +3633,7 @@
       <c r="E16" s="9" t="n"/>
       <c r="F16" s="10" t="n"/>
     </row>
-    <row r="17" ht="139" customHeight="1">
+    <row r="17" ht="184" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>エラー例</t>
@@ -3098,8 +3645,10 @@
 { "code": "E-007", "message": "出勤打刻がないため、退勤打刻できません。", "fieldErrors": [] }
 HTTP 409（退勤済み）
 { "code": "E-006", "message": "本日は既に打刻済みです。", "fieldErrors": [] }
+HTTP 409（休憩中・離席中）
+{ "code": "E-022", "message": "休憩中・離席中は退勤できません。先に休憩（離席）を終了してください。", "fieldErrors": [] }
 HTTP 401（トークンなし・期限切れ・不正。AuthenticationEntryPoint が返す JSON。Controller には到達しない）
-{ "code": "E-001", "message": "認証情報が無効、または有効期限が切れています。再度ログインしてください。", "fieldErrors": [] }</t>
+{ "code": "E-001", "message": "認証が必要です。再度ログインしてください。", "fieldErrors": [] }</t>
         </is>
       </c>
       <c r="C17" s="9" t="n"/>
@@ -3135,7 +3684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F14"/>
+  <dimension ref="A2:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3302,7 +3851,7 @@
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="10" t="n"/>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="49" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>⑥</t>
@@ -3310,23 +3859,23 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>退勤時刻を決定</t>
+          <t>継続中の休憩・離席がないか？</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>clockOut = now。ただし now が clock_in より前なら clock_in に補正（時刻補正データ対策）</t>
+          <t>AttendanceBreakRepository#findFirstByAttendanceRecordIdAndEndAtIsNull(rec.id) が空であること（rec.id が null の新規行は確認不要）</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>処理</t>
+          <t>判定（No → E-022 を返却  HTTP 409）</t>
         </is>
       </c>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="10" t="n"/>
     </row>
-    <row r="10" ht="49" customHeight="1">
+    <row r="10" ht="34" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>⑦</t>
@@ -3334,12 +3883,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>勤務・残業時間を計算</t>
+          <t>退勤時刻を決定</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>AttendanceCalculator#calculate(clock_in, clockOut) → WorkTime(workMinutes, overtimeMinutes)</t>
+          <t>clockOut = now。ただし now が clock_in より前なら clock_in に補正（時刻補正データ対策）</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -3350,7 +3899,7 @@
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="10" t="n"/>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="49" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>⑧</t>
@@ -3358,12 +3907,12 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>clock_out 等を設定し UPDATE</t>
+          <t>休憩・離席の区間を取得</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>clock_out / work_minutes / overtime_minutes を設定し saveAndFlush</t>
+          <t>spansOf(rec)：findByAttendanceRecordIdOrderByStartAtAsc → Span(kind, startAt, endAt) のリスト。区間がなければ空リスト</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -3374,7 +3923,7 @@
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="10" t="n"/>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="64" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>⑨</t>
@@ -3382,12 +3931,12 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>レスポンス返却</t>
+          <t>勤務・残業時間を計算</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>ClockOutResponse.from(record) を HTTP 200 で返す。コミットは Service メソッド終了時</t>
+          <t>AttendanceCalculator#calculate(clock_in, clockOut, spans) → WorkTime(workMinutes, overtimeMinutes)。AWAY は全て控除、BREAK は打刻合計（なければ法定休憩）を控除</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -3398,24 +3947,74 @@
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="10" t="n"/>
     </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>5.2 処理フロー図</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>⑩</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>clock_out 等を設定し UPDATE</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>clock_out / work_minutes / overtime_minutes を設定し saveAndFlush</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>処理</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>⑪</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>レスポンス返却</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>ClockOutResponse.from(record) を HTTP 200 で返す。コミットは Service メソッド終了時</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>処理</t>
+        </is>
+      </c>
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="10" t="n"/>
     </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>5.2 処理フロー図</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A16:F16"/>
     <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
     <mergeCell ref="D5:F5"/>
-    <mergeCell ref="A14:F14"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D3:F3"/>
@@ -3437,7 +4036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F80"/>
+  <dimension ref="A2:F107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3690,7 +4289,7 @@
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="10" t="n"/>
     </row>
-    <row r="18" ht="19" customHeight="1">
+    <row r="18" ht="34" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
         <is>
           <t>説明</t>
@@ -3698,7 +4297,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>本日（JST）の打刻行を行ロック付きで取得し、出勤済み・退勤未打刻であれば clock_out と勤務時間・残業時間を設定して保存する。</t>
+          <t>本日（JST）の打刻行を行ロック付きで取得し、出勤済み・退勤未打刻・継続中の休憩/離席なしであれば、clock_out と、休憩・離席を反映した勤務時間・残業時間を設定して保存する。</t>
         </is>
       </c>
       <c r="C18" s="9" t="n"/>
@@ -3778,7 +4377,7 @@
       <c r="E22" s="9" t="n"/>
       <c r="F22" s="10" t="n"/>
     </row>
-    <row r="23" ht="34" customHeight="1">
+    <row r="23" ht="49" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
           <t>例外</t>
@@ -3787,7 +4386,8 @@
       <c r="B23" s="7" t="inlineStr">
         <is>
           <t>BusinessException("E-007", "出勤打刻がないため、退勤打刻できません。", HttpStatus.CONFLICT)
-BusinessException("E-006", "本日は既に打刻済みです。", HttpStatus.CONFLICT)</t>
+BusinessException("E-006", "本日は既に打刻済みです。", HttpStatus.CONFLICT)
+BusinessException("E-022", "休憩中・離席中は退勤できません。先に休憩（離席）を終了してください。", HttpStatus.CONFLICT)</t>
         </is>
       </c>
       <c r="C23" s="9" t="n"/>
@@ -3795,7 +4395,7 @@
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="10" t="n"/>
     </row>
-    <row r="24" ht="364" customHeight="1">
+    <row r="24" ht="394" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
         <is>
           <t>処理詳細</t>
@@ -3806,27 +4406,29 @@
           <t>LocalDate today = LocalDate.now(clock);                       // ② JST の本日
 LocalDateTime now = LocalDateTime.now(clock)
         .truncatedTo(ChronoUnit.SECONDS);
-AttendanceRecord rec = attendanceRecordRepository
+AttendanceRecord rec = repository
         .findWithLockByUserIdAndWorkDate(userId, today)       // ③ FOR UPDATE
-        .orElseThrow(() -&gt; new BusinessException("E-007",     // ④ 行なし
-            "出勤打刻がないため、退勤打刻できません。", HttpStatus.CONFLICT));
-if (rec.getClockIn() == null)                                 // ④ 行はあるが clock_in なし
+        .orElse(null);
+if (rec == null || rec.getClockIn() == null)                  // ④ 行なし／clock_in なし
     throw new BusinessException("E-007",
         "出勤打刻がないため、退勤打刻できません。", HttpStatus.CONFLICT);
 if (rec.getClockOut() != null)                                // ⑤ 退勤済み
-    throw new BusinessException("E-006",
-        "本日は既に打刻済みです。", HttpStatus.CONFLICT);
-LocalDateTime clockOut = now.isBefore(rec.getClockIn())       // ⑥ 補正
+    throw alreadyStamped();                                   //    E-006「本日は既に打刻済みです。」
+if (rec.getId() != null &amp;&amp; breakRepository                    // ⑥ 休憩中・離席中
+        .findFirstByAttendanceRecordIdAndEndAtIsNull(rec.getId()).isPresent())
+    throw new BusinessException("E-022",
+        "休憩中・離席中は退勤できません。先に休憩（離席）を終了してください。", HttpStatus.CONFLICT);
+LocalDateTime out = now.isBefore(rec.getClockIn())            // ⑦ 補正
         ? rec.getClockIn() : now;
-WorkTime wt = attendanceCalculator
-        .calculate(rec.getClockIn(), clockOut);               // ⑦
-rec.setClockOut(clockOut);                                    // ⑧
+WorkTime wt = calculator.calculate(rec.getClockIn(), out,
+        spansOf(rec));                                        // ⑧ 区間取得 → ⑨ 計算
+rec.setClockOut(out);                                         // ⑩
 rec.setWorkMinutes(wt.workMinutes());
 rec.setOvertimeMinutes(wt.overtimeMinutes());
-rec = attendanceRecordRepository.saveAndFlush(rec);
+rec = repository.saveAndFlush(rec);
 log.info("Clock-out: userId={}, workDate={}, workMinutes={}, overtimeMinutes={}",
          userId, today, wt.workMinutes(), wt.overtimeMinutes());
-return ClockOutResponse.from(rec);                            // ⑨</t>
+return ClockOutResponse.from(rec);                            // ⑪</t>
         </is>
       </c>
       <c r="C24" s="9" t="n"/>
@@ -3842,7 +4444,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Clock / AttendanceRecordRepository#findWithLockByUserIdAndWorkDate / AttendanceCalculator#calculate / AttendanceRecordRepository#saveAndFlush / ClockOutResponse#from</t>
+          <t>Clock / AttendanceRecordRepository#findWithLockByUserIdAndWorkDate, saveAndFlush / AttendanceBreakRepository#findFirstByAttendanceRecordIdAndEndAtIsNull / spansOf / AttendanceCalculator#calculate / ClockOutResponse#from</t>
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
@@ -3850,7 +4452,7 @@
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="10" t="n"/>
     </row>
-    <row r="26" ht="139" customHeight="1">
+    <row r="26" ht="214" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
           <t>備考</t>
@@ -3860,9 +4462,12 @@
         <is>
           <t>【対象日】退勤できるのは「本日（JST）の work_date の行」だけ。昨日出勤して退勤を押し忘れた場合、日付が変わった後の退勤打刻は E-007 になる（日跨ぎ勤務は未対応）。退勤漏れは打刻修正申請（ONL-005 → 承認 ONL-010）で補正する。
 【二重退勤の防止】FOR UPDATE により同一行への並行更新を直列化する。2つ目のリクエストはロック解除後に clock_out ありと判定され E-006。
-【④の判定順】行なし／clock_in なし(E-007) を先に判定し、その後に clock_out あり(E-006) を判定する（SCR-102 入力チェック No.2 → No.3 の順）。
-【⑥の補正】サーバー時刻が clock_in より前になるのは、サーバー時計の巻き戻しなど異常時のみ。clock_out &lt; clock_in の行を作らないための防御で、補正時は勤務時間 0 分になる。
-【updated_at】Entity の updated_at は updatable=false のためアプリは設定しないが、UPDATE 時に DB トリガ（trg_attendance_records_updated_at / set_updated_at）が自動更新する。</t>
+【判定順】行なし／clock_in なし(E-007) → clock_out あり(E-006) → 継続中の休憩・離席あり(E-022)（SCR-102 入力チェックの順）。
+【⑦の補正】サーバー時刻が clock_in より前になるのは、サーバー時計の巻き戻しなど異常時のみ。clock_out &lt; clock_in の行を作らないための防御で、補正時は勤務時間 0 分になる。
+【updated_at】Entity の updated_at は updatable=false のためアプリは設定しないが、UPDATE 時に DB トリガ（trg_attendance_records_updated_at / set_updated_at）が自動更新する。
+【E-022】休憩・離席を終了せずに退勤すると、終了時刻のない区間が勤務時間の計算から外れて控除漏れになるため、拒否して先に終了（ONL-025）させる。画面は継続中の区間があると退勤ボタンを非活性にする（SCR-102）。
+【ロック】開始（ONL-024）・終了（ONL-025）・退勤は同じ打刻行を FOR UPDATE するため、退勤と区間の更新が同時に走っても、E-022 の判定と区間の取得は一貫した状態を見る。
+【休憩・離席の取得】退勤時に区間を 1 回だけ読み、その時点の合計で work_minutes を確定する。退勤後に区間が追加・修正された場合（修正申請 BREAK_CORRECTION の承認：ONL-010）は、その時点で再計算する。</t>
         </is>
       </c>
       <c r="C26" s="9" t="n"/>
@@ -3898,7 +4503,7 @@
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="10" t="n"/>
     </row>
-    <row r="30" ht="49" customHeight="1">
+    <row r="30" ht="79" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
           <t>シグネチャ</t>
@@ -3907,7 +4512,9 @@
       <c r="B30" s="12" t="inlineStr">
         <is>
           <t>public WorkTime calculate(LocalDateTime clockIn, LocalDateTime clockOut)
-public record WorkTime(int workMinutes, int overtimeMinutes) {}</t>
+public WorkTime calculate(LocalDateTime clockIn, LocalDateTime clockOut, List&lt;Span&gt; spans)
+public record WorkTime(int workMinutes, int overtimeMinutes) {}
+public record Span(String kind, LocalDateTime start, LocalDateTime end) {}</t>
         </is>
       </c>
       <c r="C30" s="9" t="n"/>
@@ -3915,7 +4522,7 @@
       <c r="E30" s="9" t="n"/>
       <c r="F30" s="10" t="n"/>
     </row>
-    <row r="31" ht="19" customHeight="1">
+    <row r="31" ht="34" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
           <t>説明</t>
@@ -3923,7 +4530,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>出勤・退勤時刻から、休憩を控除した勤務時間（分）と残業時間（分）を計算する。状態を持たない純粋な計算（DB アクセス・現在時刻取得なし）。</t>
+          <t>出勤・退勤時刻と、休憩・日中離席の区間から、勤務時間（分）と残業時間（分）を計算する。状態を持たない純粋な計算（DB アクセス・現在時刻取得なし）。2 引数版は区間なし（空リスト）で 3 引数版に委譲する。</t>
         </is>
       </c>
       <c r="C31" s="9" t="n"/>
@@ -4009,17 +4616,21 @@
       <c r="F35" s="10" t="n"/>
     </row>
     <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>戻り値</t>
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>spans</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>WorkTime(workMinutes, overtimeMinutes)。どちらも 0 以上</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="n"/>
+          <t>List&lt;Span&gt;</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席の区間（kind = BREAK / AWAY。end が null の区間は計算対象外）。空リスト可</t>
+        </is>
+      </c>
       <c r="D36" s="9" t="n"/>
       <c r="E36" s="9" t="n"/>
       <c r="F36" s="10" t="n"/>
@@ -4027,12 +4638,12 @@
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>例外</t>
+          <t>戻り値</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>なし（clockOut が clockIn より前なら 0 分扱い）</t>
+          <t>WorkTime(workMinutes, overtimeMinutes)。どちらも 0 以上</t>
         </is>
       </c>
       <c r="C37" s="9" t="n"/>
@@ -4040,23 +4651,15 @@
       <c r="E37" s="9" t="n"/>
       <c r="F37" s="10" t="n"/>
     </row>
-    <row r="38" ht="139" customHeight="1">
+    <row r="38" ht="19" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>処理詳細</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>long gross = Duration.between(
-        clockIn.truncatedTo(ChronoUnit.MINUTES),
-        clockOut.truncatedTo(ChronoUnit.MINUTES)).toMinutes();   // 拘束時間(分)。秒は切り捨て
-if (gross &lt; 0) gross = 0;
-int breakMinutes = gross &gt; THRESHOLD_8H ? BREAK_OVER_8H           // 8時間超 → 60分
-                 : gross &gt; THRESHOLD_6H ? BREAK_OVER_6H : 0;      // 6時間超 → 45分
-int work = (int) (gross - breakMinutes);                          // 勤務時間(分)
-int overtime = Math.max(0, work - STANDARD_MINUTES);              // 残業(分)
-return new WorkTime(work, overtime);</t>
+          <t>例外</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>なし（clockOut が clockIn より前なら 0 分扱い）</t>
         </is>
       </c>
       <c r="C38" s="9" t="n"/>
@@ -4064,15 +4667,35 @@
       <c r="E38" s="9" t="n"/>
       <c r="F38" s="10" t="n"/>
     </row>
-    <row r="39" ht="19" customHeight="1">
+    <row r="39" ht="319" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>呼出先</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>なし</t>
+          <t>処理詳細</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
+        <is>
+          <t>LocalDateTime in  = clockIn.truncatedTo(ChronoUnit.MINUTES);
+LocalDateTime out = clockOut.truncatedTo(ChronoUnit.MINUTES);
+long gross = Duration.between(in, out).toMinutes();         // 拘束時間(分)。秒は切り捨て
+if (gross &lt; 0) gross = 0;
+long recordedBreak = 0, away = 0;
+for (Span sp : spans) {
+    if (sp.end() == null) continue;                          // 継続中の区間は数えない
+    LocalDateTime s = sp.start().truncatedTo(MINUTES), e = sp.end().truncatedTo(MINUTES);
+    if (s.isBefore(in)) s = in;                              // 出勤〜退勤の範囲に切り詰める
+    if (e.isAfter(out)) e = out;
+    long m = Duration.between(s, e).toMinutes();
+    if (m &lt;= 0) continue;
+    if ("AWAY".equals(sp.kind())) away += m; else recordedBreak += m;
+}
+long net = gross - away;                                     // 離席を引いた実拘束時間
+int statutory = net &gt; THRESHOLD_8H ? BREAK_OVER_8H           // 8時間超 → 60分
+              : net &gt; THRESHOLD_6H ? BREAK_OVER_6H : 0;      // 6時間超 → 45分
+long breakMinutes = recordedBreak &gt; 0 ? recordedBreak : statutory;   // 休憩を打刻した日は打刻どおり
+int work = (int) Math.max(0, net - breakMinutes);            // 勤務時間(分)
+int overtime = Math.max(0, work - STANDARD_MINUTES);         // 残業(分)
+return new WorkTime(work, overtime);</t>
         </is>
       </c>
       <c r="C39" s="9" t="n"/>
@@ -4080,18 +4703,15 @@
       <c r="E39" s="9" t="n"/>
       <c r="F39" s="10" t="n"/>
     </row>
-    <row r="40" ht="94" customHeight="1">
+    <row r="40" ht="19" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>呼出先</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>休憩は「6時間超 → 45分、8時間超 → 60分」を自動控除する（労基法第34条）。「超」なので 360 分ちょうどは控除なし、480 分ちょうどは 45 分控除。
-残業は勤務時間（休憩控除後）が 480 分を超えた分。したがって 09:00〜18:00（拘束540分・休憩60分・勤務480分）の残業は 0 分で、18:30 退勤で 30 分。
-深夜・休日の割増計算は行わない。画面設計書(SCR-103)の表示例の数値は目安であり、本規則（KF-DD-001）を正とする。
-計算例は下の表（6.x）を参照。</t>
+          <t>なし</t>
         </is>
       </c>
       <c r="C40" s="9" t="n"/>
@@ -4099,29 +4719,34 @@
       <c r="E40" s="9" t="n"/>
       <c r="F40" s="10" t="n"/>
     </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>6.4  ClockOutResponse#from</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="n"/>
-      <c r="C42" s="9" t="n"/>
-      <c r="D42" s="9" t="n"/>
-      <c r="E42" s="9" t="n"/>
-      <c r="F42" s="10" t="n"/>
-    </row>
-    <row r="43" ht="19" customHeight="1">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>DTO（record）静的ファクトリ</t>
-        </is>
-      </c>
+    <row r="41" ht="154" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>【離席（AWAY）】全て控除する（私用外出など）。控除後の実拘束時間 net で法定休憩のしきい値を判定する。
+【休憩（BREAK）】1 回でも打刻した日（出勤〜退勤の範囲内の合計が 1 分以上）は、打刻した合計を控除する（法定休憩より短くてもそのまま控除。補正しない）。休憩の打刻がない日だけ、法定休憩「6時間超 → 45分、8時間超 → 60分」（労基法第34条）を自動控除する。「超」なので 360 分ちょうどは控除なし、480 分ちょうどは 45 分控除。
+【区間なし】spans が空なら従来どおり（拘束時間に対する法定休憩の自動控除）。ONL-010 の打刻修正の反映でも、その日の区間を渡して再計算する。
+【継続中の区間】end が null の区間は計算に入れない（通常は E-022 により退勤時には存在しない。修正申請の承認などで継続中のまま再計算される場合の保護）。
+残業は勤務時間（休憩・離席控除後）が 480 分を超えた分。したがって 09:00〜18:00・休憩 60 分なら勤務 480 分・残業 0 分。
+深夜・休日の割増計算は行わない。計算例は下の表（6.x）を参照。</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="10" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>6.4  AttendanceService#spansOf</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n"/>
       <c r="C43" s="9" t="n"/>
       <c r="D43" s="9" t="n"/>
       <c r="E43" s="9" t="n"/>
@@ -4130,12 +4755,12 @@
     <row r="44" ht="19" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>シグネチャ</t>
-        </is>
-      </c>
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>public static ClockOutResponse from(AttendanceRecord rec)</t>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Service 内部メソッド（ONL-003 / 010 の計算で共用）</t>
         </is>
       </c>
       <c r="C44" s="9" t="n"/>
@@ -4146,12 +4771,12 @@
     <row r="45" ht="19" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>AttendanceRecord から応答 DTO を作る。</t>
+          <t>シグネチャ</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>private List&lt;AttendanceCalculator.Span&gt; spansOf(AttendanceRecord rec)</t>
         </is>
       </c>
       <c r="C45" s="9" t="n"/>
@@ -4162,12 +4787,12 @@
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>アノテーション</t>
+          <t>説明</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>record ClockOutResponse(String clockOut, Integer workMinutes, Integer overtimeMinutes)</t>
+          <t>打刻行の休憩・離席の区間を start_at 昇順で取得し、計算用の Span に変換する。</t>
         </is>
       </c>
       <c r="C46" s="9" t="n"/>
@@ -4176,39 +4801,35 @@
       <c r="F46" s="10" t="n"/>
     </row>
     <row r="47" ht="19" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>引数名</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
+      <c r="A47" s="11" t="inlineStr">
+        <is>
+          <t>アノテーション</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>なし（呼出し元の @Transactional に参加）</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="n"/>
       <c r="D47" s="9" t="n"/>
       <c r="E47" s="9" t="n"/>
       <c r="F47" s="10" t="n"/>
     </row>
     <row r="48" ht="19" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>rec</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>AttendanceRecord</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>更新済みの打刻行（clockOut / workMinutes / overtimeMinutes は非 NULL）</t>
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>引数名</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="D48" s="9" t="n"/>
@@ -4216,17 +4837,21 @@
       <c r="F48" s="10" t="n"/>
     </row>
     <row r="49" ht="19" customHeight="1">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>戻り値</t>
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>rec</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>ClockOutResponse</t>
-        </is>
-      </c>
-      <c r="C49" s="9" t="n"/>
+          <t>AttendanceRecord</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>対象の打刻行</t>
+        </is>
+      </c>
       <c r="D49" s="9" t="n"/>
       <c r="E49" s="9" t="n"/>
       <c r="F49" s="10" t="n"/>
@@ -4234,12 +4859,12 @@
     <row r="50" ht="19" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>例外</t>
+          <t>戻り値</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>List&lt;AttendanceCalculator.Span&gt;。区間がなければ空リスト</t>
         </is>
       </c>
       <c r="C50" s="9" t="n"/>
@@ -4247,13 +4872,228 @@
       <c r="E50" s="9" t="n"/>
       <c r="F50" s="10" t="n"/>
     </row>
-    <row r="51" ht="64" customHeight="1">
+    <row r="51" ht="19" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
+          <t>例外</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="n"/>
+      <c r="D51" s="9" t="n"/>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="10" t="n"/>
+    </row>
+    <row r="52" ht="64" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
           <t>処理詳細</t>
         </is>
       </c>
-      <c r="B51" s="12" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>if (rec.getId() == null) return List.of();                      // 未保存の行は区間なし
+return breakRepository.findByAttendanceRecordIdOrderByStartAtAsc(rec.getId()).stream()
+    .map(b -&gt; new AttendanceCalculator.Span(b.getKind(), b.getStartAt(), b.getEndAt()))
+    .toList();</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="n"/>
+      <c r="D52" s="9" t="n"/>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="10" t="n"/>
+    </row>
+    <row r="53" ht="19" customHeight="1">
+      <c r="A53" s="11" t="inlineStr">
+        <is>
+          <t>呼出先</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>AttendanceBreakRepository#findByAttendanceRecordIdOrderByStartAtAsc</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="n"/>
+      <c r="D53" s="9" t="n"/>
+      <c r="E53" s="9" t="n"/>
+      <c r="F53" s="10" t="n"/>
+    </row>
+    <row r="54" ht="19" customHeight="1">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>終了していない区間（end_at が NULL）も Span に含まれるが、calculate が無視する。</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="n"/>
+      <c r="D54" s="9" t="n"/>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="10" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>6.5  ClockOutResponse#from</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="n"/>
+      <c r="C56" s="9" t="n"/>
+      <c r="D56" s="9" t="n"/>
+      <c r="E56" s="9" t="n"/>
+      <c r="F56" s="10" t="n"/>
+    </row>
+    <row r="57" ht="19" customHeight="1">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>DTO（record）静的ファクトリ</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="9" t="n"/>
+      <c r="E57" s="9" t="n"/>
+      <c r="F57" s="10" t="n"/>
+    </row>
+    <row r="58" ht="19" customHeight="1">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>シグネチャ</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>public static ClockOutResponse from(AttendanceRecord rec)</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="n"/>
+      <c r="D58" s="9" t="n"/>
+      <c r="E58" s="9" t="n"/>
+      <c r="F58" s="10" t="n"/>
+    </row>
+    <row r="59" ht="19" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>AttendanceRecord から応答 DTO を作る。</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="n"/>
+      <c r="D59" s="9" t="n"/>
+      <c r="E59" s="9" t="n"/>
+      <c r="F59" s="10" t="n"/>
+    </row>
+    <row r="60" ht="19" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>アノテーション</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>record ClockOutResponse(String clockOut, Integer workMinutes, Integer overtimeMinutes)</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="n"/>
+      <c r="D60" s="9" t="n"/>
+      <c r="E60" s="9" t="n"/>
+      <c r="F60" s="10" t="n"/>
+    </row>
+    <row r="61" ht="19" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>引数名</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="n"/>
+      <c r="E61" s="9" t="n"/>
+      <c r="F61" s="10" t="n"/>
+    </row>
+    <row r="62" ht="19" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>rec</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>AttendanceRecord</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>更新済みの打刻行（clockOut / workMinutes / overtimeMinutes は非 NULL）</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="n"/>
+      <c r="E62" s="9" t="n"/>
+      <c r="F62" s="10" t="n"/>
+    </row>
+    <row r="63" ht="19" customHeight="1">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>戻り値</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>ClockOutResponse</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="n"/>
+      <c r="D63" s="9" t="n"/>
+      <c r="E63" s="9" t="n"/>
+      <c r="F63" s="10" t="n"/>
+    </row>
+    <row r="64" ht="19" customHeight="1">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>例外</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="n"/>
+      <c r="D64" s="9" t="n"/>
+      <c r="E64" s="9" t="n"/>
+      <c r="F64" s="10" t="n"/>
+    </row>
+    <row r="65" ht="64" customHeight="1">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>処理詳細</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
         <is>
           <t>return new ClockOutResponse(
     AppTime.toIso(rec.getClockOut()),       // 2026-10-03T18:30:00+09:00
@@ -4261,223 +5101,6 @@
     rec.getOvertimeMinutes());</t>
         </is>
       </c>
-      <c r="C51" s="9" t="n"/>
-      <c r="D51" s="9" t="n"/>
-      <c r="E51" s="9" t="n"/>
-      <c r="F51" s="10" t="n"/>
-    </row>
-    <row r="52" ht="19" customHeight="1">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>呼出先</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>AppTime#toIso</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="n"/>
-      <c r="D52" s="9" t="n"/>
-      <c r="E52" s="9" t="n"/>
-      <c r="F52" s="10" t="n"/>
-    </row>
-    <row r="53" ht="19" customHeight="1">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>JSON キーは camelCase。</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="n"/>
-      <c r="D53" s="9" t="n"/>
-      <c r="E53" s="9" t="n"/>
-      <c r="F53" s="10" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>6.5  AttendanceRecordRepository#findWithLockByUserIdAndWorkDate</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="n"/>
-      <c r="C55" s="9" t="n"/>
-      <c r="D55" s="9" t="n"/>
-      <c r="E55" s="9" t="n"/>
-      <c r="F55" s="10" t="n"/>
-    </row>
-    <row r="56" ht="19" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Repository（ONL-002 で定義済み・本処理で再利用）</t>
-        </is>
-      </c>
-      <c r="C56" s="9" t="n"/>
-      <c r="D56" s="9" t="n"/>
-      <c r="E56" s="9" t="n"/>
-      <c r="F56" s="10" t="n"/>
-    </row>
-    <row r="57" ht="34" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>シグネチャ</t>
-        </is>
-      </c>
-      <c r="B57" s="12" t="inlineStr">
-        <is>
-          <t>@Lock(LockModeType.PESSIMISTIC_WRITE)
-Optional&lt;AttendanceRecord&gt; findWithLockByUserIdAndWorkDate(Long userId, LocalDate workDate)</t>
-        </is>
-      </c>
-      <c r="C57" s="9" t="n"/>
-      <c r="D57" s="9" t="n"/>
-      <c r="E57" s="9" t="n"/>
-      <c r="F57" s="10" t="n"/>
-    </row>
-    <row r="58" ht="19" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>本日の打刻行を行ロック付きで1件返す。メソッドの追加・変更はない。</t>
-        </is>
-      </c>
-      <c r="C58" s="9" t="n"/>
-      <c r="D58" s="9" t="n"/>
-      <c r="E58" s="9" t="n"/>
-      <c r="F58" s="10" t="n"/>
-    </row>
-    <row r="59" ht="19" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>アノテーション</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>@Lock(LockModeType.PESSIMISTIC_WRITE)</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="n"/>
-      <c r="D59" s="9" t="n"/>
-      <c r="E59" s="9" t="n"/>
-      <c r="F59" s="10" t="n"/>
-    </row>
-    <row r="60" ht="19" customHeight="1">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>引数名</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>型</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="D60" s="9" t="n"/>
-      <c r="E60" s="9" t="n"/>
-      <c r="F60" s="10" t="n"/>
-    </row>
-    <row r="61" ht="19" customHeight="1">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>userId</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>ユーザーID</t>
-        </is>
-      </c>
-      <c r="D61" s="9" t="n"/>
-      <c r="E61" s="9" t="n"/>
-      <c r="F61" s="10" t="n"/>
-    </row>
-    <row r="62" ht="19" customHeight="1">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>workDate</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>LocalDate</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>勤務日（今日の JST 日付）</t>
-        </is>
-      </c>
-      <c r="D62" s="9" t="n"/>
-      <c r="E62" s="9" t="n"/>
-      <c r="F62" s="10" t="n"/>
-    </row>
-    <row r="63" ht="19" customHeight="1">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t>戻り値</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>Optional&lt;AttendanceRecord&gt;</t>
-        </is>
-      </c>
-      <c r="C63" s="9" t="n"/>
-      <c r="D63" s="9" t="n"/>
-      <c r="E63" s="9" t="n"/>
-      <c r="F63" s="10" t="n"/>
-    </row>
-    <row r="64" ht="19" customHeight="1">
-      <c r="A64" s="11" t="inlineStr">
-        <is>
-          <t>例外</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>ロック待ちタイムアウト → PessimisticLockingFailureException → E-012</t>
-        </is>
-      </c>
-      <c r="C64" s="9" t="n"/>
-      <c r="D64" s="9" t="n"/>
-      <c r="E64" s="9" t="n"/>
-      <c r="F64" s="10" t="n"/>
-    </row>
-    <row r="65" ht="19" customHeight="1">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t>処理詳細</t>
-        </is>
-      </c>
-      <c r="B65" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date = ? FOR UPDATE</t>
-        </is>
-      </c>
       <c r="C65" s="9" t="n"/>
       <c r="D65" s="9" t="n"/>
       <c r="E65" s="9" t="n"/>
@@ -4491,7 +5114,7 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>（DB: attendance_records）</t>
+          <t>AppTime#toIso</t>
         </is>
       </c>
       <c r="C66" s="9" t="n"/>
@@ -4507,7 +5130,7 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>本処理では行が存在する場合のみロックが取れる（存在しなければ E-007）。</t>
+          <t>JSON キーは camelCase。</t>
         </is>
       </c>
       <c r="C67" s="9" t="n"/>
@@ -4518,7 +5141,7 @@
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>6.6  AttendanceCalculator#calculate の計算例（単体テストの期待値）</t>
+          <t>6.6  AttendanceRecordRepository#findWithLockByUserIdAndWorkDate</t>
         </is>
       </c>
       <c r="B69" s="9" t="n"/>
@@ -4528,422 +5151,1017 @@
       <c r="F69" s="10" t="n"/>
     </row>
     <row r="70" ht="19" customHeight="1">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>出勤</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>退勤</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>拘束(分)</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>休憩(分)</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>勤務(分)</t>
-        </is>
-      </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>残業(分)</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="19" customHeight="1">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Repository（ONL-002 で定義済み・本処理で再利用）</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="n"/>
+      <c r="D70" s="9" t="n"/>
+      <c r="E70" s="9" t="n"/>
+      <c r="F70" s="10" t="n"/>
+    </row>
+    <row r="71" ht="34" customHeight="1">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>シグネチャ</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>@Lock(LockModeType.PESSIMISTIC_WRITE)
+Optional&lt;AttendanceRecord&gt; findWithLockByUserIdAndWorkDate(Long userId, LocalDate workDate)</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="n"/>
+      <c r="D71" s="9" t="n"/>
+      <c r="E71" s="9" t="n"/>
+      <c r="F71" s="10" t="n"/>
     </row>
     <row r="72" ht="19" customHeight="1">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t>09:00</t>
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>本日の打刻行を行ロック付きで1件返す。メソッドの追加・変更はない。</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="n"/>
+      <c r="D72" s="9" t="n"/>
+      <c r="E72" s="9" t="n"/>
+      <c r="F72" s="10" t="n"/>
     </row>
     <row r="73" ht="19" customHeight="1">
-      <c r="A73" s="7" t="inlineStr">
-        <is>
-          <t>09:00</t>
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>アノテーション</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="C73" s="7" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>@Lock(LockModeType.PESSIMISTIC_WRITE)</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="n"/>
+      <c r="D73" s="9" t="n"/>
+      <c r="E73" s="9" t="n"/>
+      <c r="F73" s="10" t="n"/>
     </row>
     <row r="74" ht="19" customHeight="1">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C74" s="7" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>435</t>
-        </is>
-      </c>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>引数名</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>型</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="n"/>
+      <c r="E74" s="9" t="n"/>
+      <c r="F74" s="10" t="n"/>
     </row>
     <row r="75" ht="19" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>userId</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>481</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
-      </c>
-      <c r="F75" s="7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>ユーザーID</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="n"/>
+      <c r="E75" s="9" t="n"/>
+      <c r="F75" s="10" t="n"/>
     </row>
     <row r="76" ht="19" customHeight="1">
       <c r="A76" s="7" t="inlineStr">
         <is>
+          <t>workDate</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>LocalDate</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>勤務日（今日の JST 日付）</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="n"/>
+      <c r="E76" s="9" t="n"/>
+      <c r="F76" s="10" t="n"/>
+    </row>
+    <row r="77" ht="19" customHeight="1">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>戻り値</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Optional&lt;AttendanceRecord&gt;</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="n"/>
+      <c r="D77" s="9" t="n"/>
+      <c r="E77" s="9" t="n"/>
+      <c r="F77" s="10" t="n"/>
+    </row>
+    <row r="78" ht="19" customHeight="1">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t>例外</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>ロック待ちタイムアウト → PessimisticLockingFailureException → E-012</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="n"/>
+      <c r="D78" s="9" t="n"/>
+      <c r="E78" s="9" t="n"/>
+      <c r="F78" s="10" t="n"/>
+    </row>
+    <row r="79" ht="19" customHeight="1">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>処理詳細</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date = ? FOR UPDATE</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="n"/>
+      <c r="D79" s="9" t="n"/>
+      <c r="E79" s="9" t="n"/>
+      <c r="F79" s="10" t="n"/>
+    </row>
+    <row r="80" ht="19" customHeight="1">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>呼出先</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>（DB: attendance_records）</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="n"/>
+      <c r="D80" s="9" t="n"/>
+      <c r="E80" s="9" t="n"/>
+      <c r="F80" s="10" t="n"/>
+    </row>
+    <row r="81" ht="19" customHeight="1">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>本処理では行が存在する場合のみロックが取れる（存在しなければ E-007）。</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="n"/>
+      <c r="D81" s="9" t="n"/>
+      <c r="E81" s="9" t="n"/>
+      <c r="F81" s="10" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>6.7  AttendanceCalculator#calculate の計算例①：区間なし（休憩の打刻なし。単体テストの期待値）</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="n"/>
+      <c r="C83" s="9" t="n"/>
+      <c r="D83" s="9" t="n"/>
+      <c r="E83" s="9" t="n"/>
+      <c r="F83" s="10" t="n"/>
+    </row>
+    <row r="84" ht="19" customHeight="1">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>出勤</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>退勤</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>拘束(分)</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>休憩(分)</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>勤務(分)</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>残業(分)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="19" customHeight="1">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="19" customHeight="1">
+      <c r="A86" s="7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="19" customHeight="1">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="19" customHeight="1">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="19" customHeight="1">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="19" customHeight="1">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>540</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="F76" s="7" t="inlineStr">
+      <c r="F90" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="19" customHeight="1">
-      <c r="A77" s="7" t="inlineStr">
+    <row r="91" ht="19" customHeight="1">
+      <c r="A91" s="7" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>18:01</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
         <is>
           <t>541</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
+      <c r="E91" s="7" t="inlineStr">
         <is>
           <t>481</t>
         </is>
       </c>
-      <c r="F77" s="7" t="inlineStr">
+      <c r="F91" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="19" customHeight="1">
-      <c r="A78" s="7" t="inlineStr">
+    <row r="92" ht="19" customHeight="1">
+      <c r="A92" s="7" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B92" s="7" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C92" s="7" t="inlineStr">
         <is>
           <t>570</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
+      <c r="D92" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
+      <c r="E92" s="7" t="inlineStr">
         <is>
           <t>510</t>
         </is>
       </c>
-      <c r="F78" s="7" t="inlineStr">
+      <c r="F92" s="7" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="19" customHeight="1">
-      <c r="A79" s="7" t="inlineStr">
+    <row r="93" ht="19" customHeight="1">
+      <c r="A93" s="7" t="inlineStr">
         <is>
           <t>09:00:59</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
+      <c r="B93" s="7" t="inlineStr">
         <is>
           <t>18:00:00</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>540（秒切捨て）</t>
         </is>
       </c>
-      <c r="D79" s="7" t="inlineStr">
+      <c r="D93" s="7" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="F79" s="7" t="inlineStr">
+      <c r="F93" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="19" customHeight="1">
-      <c r="A80" s="7" t="inlineStr">
+    <row r="94" ht="19" customHeight="1">
+      <c r="A94" s="7" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="B80" s="7" t="inlineStr">
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>09:00（退勤が前）</t>
         </is>
       </c>
-      <c r="C80" s="7" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>0（負は0）</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr">
+      <c r="D94" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E80" s="7" t="inlineStr">
+      <c r="E94" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F80" s="7" t="inlineStr">
+      <c r="F94" s="7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>6.8  AttendanceCalculator#calculate の計算例②：休憩・離席の区間あり（出勤 09:00 固定）</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="n"/>
+      <c r="C96" s="9" t="n"/>
+      <c r="D96" s="9" t="n"/>
+      <c r="E96" s="9" t="n"/>
+      <c r="F96" s="10" t="n"/>
+    </row>
+    <row r="97" ht="19" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>退勤</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>区間</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>拘束(分)</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>離席(分)</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>休憩(分)</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>勤務(分)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="19" customHeight="1">
+      <c r="A98" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>BREAK 12:00-13:00</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>60（打刻）</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="34" customHeight="1">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>BREAK 12:00-12:30（法定60分より短い）</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>30（打刻）</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="19" customHeight="1">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>60（法定・自動）</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="34" customHeight="1">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>AWAY 14:00-15:00（休憩の打刻なし）</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>45（法定・net=480）</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="34" customHeight="1">
+      <c r="A102" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>BREAK 12:00-13:00 ＋ AWAY 15:00-15:30</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>60（打刻）</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="34" customHeight="1">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>BREAK 12:00-14:00（長い休憩）</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>120（打刻）</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="34" customHeight="1">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>BREAK 12:00-（継続中・end=NULL）</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>60（法定。継続中は数えない）</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="34" customHeight="1">
+      <c r="A105" s="7" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>BREAK 12:00-13:00（退勤で切り詰め）</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>30（12:00-12:30）</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="34" customHeight="1">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>AWAY 11:00-12:30（離席で net が 6 時間以下）</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>0（net=330 ≦ 360）</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="34" customHeight="1">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>BREAK 08:00-08:30（出勤前。範囲外）</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>60（法定。範囲外は 0 分）</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="63">
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="C48:F48"/>
+  <mergeCells count="77">
     <mergeCell ref="C61:F61"/>
-    <mergeCell ref="C8:F8"/>
     <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B81:F81"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B71:F71"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="B72:F72"/>
+    <mergeCell ref="B70:F70"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="C76:F76"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="C8:F8"/>
     <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="C48:F48"/>
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="C7:F7"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B46:F46"/>
     <mergeCell ref="B22:F22"/>
-    <mergeCell ref="A55:F55"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B56:F56"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="A69:F69"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C62:F62"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="C49:F49"/>
     <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B23:F23"/>
     <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="A96:F96"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="C74:F74"/>
     <mergeCell ref="B29:F29"/>
-    <mergeCell ref="A28:F28"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="C35:F35"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="C47:F47"/>
+    <mergeCell ref="B78:F78"/>
     <mergeCell ref="B40:F40"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B65:F65"/>
-    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="C75:F75"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B5:F5"/>
     <mergeCell ref="B51:F51"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B79:F79"/>
     <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="C60:F60"/>
-    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="B41:F41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4956,7 +6174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F23"/>
+  <dimension ref="A2:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5311,175 +6529,414 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>■ attendance_breaks</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>DB列</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Entityフィールド</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Java型</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>この処理での使用</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>attendance_record_id</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>attendanceRecordId</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>○ 検索条件（継続中の確認・区間の取得）</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>FK attendance_records(id)。idx_attendance_breaks_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="49" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>○ 計算の入力（AWAY は離席、それ以外は休憩）</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>BREAK / AWAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>start_at</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>startAt</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>LocalDateTime</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>○ 計算の入力・並び順</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>TIMESTAMP（JST）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="49" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>end_at</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>endAt</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>LocalDateTime</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>○ 継続中の判定（IS NULL）・計算の入力（NULL は対象外）</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>NULL = 継続中</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>id / created_at / updated_at</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>id / createdAt / updatedAt</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>— 参照しない（本処理は読取りのみ）</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>詳細は ONL-024 の 7.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>7.2 SQL・クエリ</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="10" t="n"/>
-    </row>
-    <row r="16" ht="79" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="79" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>打刻行の検索・行ロック（AttendanceRecordRepository#findWithLockByUserIdAndWorkDate）</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date = ? FOR UPDATE</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="10" t="n"/>
-    </row>
-    <row r="17" ht="64" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="79" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>継続中の区間の確認（AttendanceBreakRepository#findFirstByAttendanceRecordIdAndEndAtIsNull）</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM attendance_breaks WHERE attendance_record_id = ? AND end_at IS NULL LIMIT 1</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="79" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>区間の取得（AttendanceBreakRepository#findByAttendanceRecordIdOrderByStartAtAsc）</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM attendance_breaks WHERE attendance_record_id = ? ORDER BY start_at</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="64" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>退勤の更新（saveAndFlush）</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>UPDATE attendance_records SET user_id = ?, work_date = ?, clock_in = ?, clock_out = ?, work_minutes = ?, overtime_minutes = ? WHERE id = ?
   -- 変更されるのは clock_out / work_minutes / overtime_minutes の3列（Hibernate 既定で全列を SET する）。updated_at は SET しない（DB トリガで自動）</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="10" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="10" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>7.3 設定値</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="10" t="n"/>
-    </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>キー</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>格納場所</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="F20" s="10" t="n"/>
-    </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="F29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>（定数）STANDARD_MINUTES</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>AttendanceCalculator</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>所定労働時間（分）。変更時は本書と KF-DD-001 を改訂</t>
         </is>
       </c>
-      <c r="F21" s="10" t="n"/>
-    </row>
-    <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="F30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>（定数）BREAK_OVER_6H / BREAK_OVER_8H</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>AttendanceCalculator</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>45 / 60</t>
         </is>
       </c>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>休憩控除（分）。しきい値は 360 / 480 分</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="n"/>
-    </row>
-    <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>法定休憩（分）。しきい値は 360 / 480 分。休憩の打刻がない日だけ適用（打刻がある日は打刻合計を控除）</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>（Bean）Clock</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>config/ClockConfig.java</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Clock.system(Asia/Tokyo)</t>
         </is>
       </c>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>ONL-002 で定義。DB のタイムゾーン設定も ONL-002 の 7.3 を参照</t>
         </is>
       </c>
-      <c r="F23" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="17">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="B23:F23"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="E31:F31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
